--- a/Documents/Product Catalog/Office/Officer Chair  Specifications.xlsx
+++ b/Documents/Product Catalog/Office/Officer Chair  Specifications.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Product Price List\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="d:\Talukder Furniture\Documents\Product Catalog\Office\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D56579A6-DCF1-4AFD-A1B4-181716D71FD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12435"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Officer Chair  " sheetId="13" r:id="rId1"/>
@@ -17,7 +18,7 @@
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'Officer Chair  '!$B$1:$R$17</definedName>
   </definedNames>
-  <calcPr calcId="152511"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -26,6 +27,8 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -487,7 +490,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="13">
     <font>
       <sz val="10"/>
@@ -790,46 +793,46 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="1" fontId="9" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="1" fontId="9" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="9" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="1" fontId="9" fillId="4" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -869,7 +872,7 @@
         <xdr:cNvPr id="2" name="image1.jpeg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0100-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -919,7 +922,7 @@
         <xdr:cNvPr id="95" name="image93.jpeg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0100-0000B3010000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-0000B3010000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -969,7 +972,7 @@
         <xdr:cNvPr id="96" name="image94.jpeg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0100-0000B4010000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-0000B4010000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1019,7 +1022,7 @@
         <xdr:cNvPr id="97" name="image95.jpeg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0100-0000B5010000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-0000B5010000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1069,7 +1072,7 @@
         <xdr:cNvPr id="98" name="image96.jpeg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0100-0000B6010000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-0000B6010000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1119,7 +1122,7 @@
         <xdr:cNvPr id="99" name="image97.jpeg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0100-0000B7010000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-0000B7010000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1169,7 +1172,7 @@
         <xdr:cNvPr id="100" name="image98.jpeg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0100-0000B8010000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-0000B8010000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1219,7 +1222,7 @@
         <xdr:cNvPr id="101" name="image99.jpeg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0100-0000B9010000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-0000B9010000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1269,7 +1272,7 @@
         <xdr:cNvPr id="102" name="image100.jpeg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0100-0000BA010000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-0000BA010000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1319,7 +1322,7 @@
         <xdr:cNvPr id="103" name="image101.jpeg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0100-0000BB010000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-0000BB010000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1369,7 +1372,7 @@
         <xdr:cNvPr id="104" name="image102.jpeg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0100-0000BC010000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-0000BC010000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1419,7 +1422,7 @@
         <xdr:cNvPr id="105" name="image103.jpeg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0100-0000BD010000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-0000BD010000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1469,7 +1472,7 @@
         <xdr:cNvPr id="109" name="image107.jpeg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0100-0000C1010000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-0000C1010000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1505,9 +1508,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1545,9 +1548,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1582,7 +1585,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1617,7 +1620,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1790,7 +1793,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="B1:AT17"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
@@ -1813,89 +1816,89 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:46" ht="39.950000000000003" customHeight="1">
-      <c r="B1" s="21" t="s">
+      <c r="B1" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="21"/>
-      <c r="D1" s="21"/>
-      <c r="E1" s="21"/>
-      <c r="F1" s="21"/>
-      <c r="G1" s="21"/>
-      <c r="H1" s="21"/>
-      <c r="I1" s="21"/>
-      <c r="J1" s="21"/>
-      <c r="K1" s="21"/>
-      <c r="L1" s="21"/>
-      <c r="M1" s="21"/>
-      <c r="N1" s="21"/>
-      <c r="O1" s="21"/>
-      <c r="P1" s="21"/>
-      <c r="Q1" s="21"/>
-      <c r="R1" s="22"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="15"/>
+      <c r="G1" s="15"/>
+      <c r="H1" s="15"/>
+      <c r="I1" s="15"/>
+      <c r="J1" s="15"/>
+      <c r="K1" s="15"/>
+      <c r="L1" s="15"/>
+      <c r="M1" s="15"/>
+      <c r="N1" s="15"/>
+      <c r="O1" s="15"/>
+      <c r="P1" s="15"/>
+      <c r="Q1" s="15"/>
+      <c r="R1" s="16"/>
     </row>
     <row r="2" spans="2:46" ht="39.950000000000003" customHeight="1">
-      <c r="B2" s="23" t="s">
+      <c r="B2" s="17" t="s">
         <v>42</v>
       </c>
-      <c r="C2" s="23"/>
-      <c r="D2" s="23"/>
-      <c r="E2" s="23"/>
-      <c r="F2" s="23"/>
-      <c r="G2" s="23"/>
-      <c r="H2" s="23"/>
-      <c r="I2" s="23"/>
-      <c r="J2" s="23"/>
-      <c r="K2" s="23"/>
-      <c r="L2" s="23"/>
-      <c r="M2" s="23"/>
-      <c r="N2" s="23"/>
-      <c r="O2" s="23"/>
-      <c r="P2" s="23"/>
-      <c r="Q2" s="23"/>
-      <c r="R2" s="24"/>
+      <c r="C2" s="17"/>
+      <c r="D2" s="17"/>
+      <c r="E2" s="17"/>
+      <c r="F2" s="17"/>
+      <c r="G2" s="17"/>
+      <c r="H2" s="17"/>
+      <c r="I2" s="17"/>
+      <c r="J2" s="17"/>
+      <c r="K2" s="17"/>
+      <c r="L2" s="17"/>
+      <c r="M2" s="17"/>
+      <c r="N2" s="17"/>
+      <c r="O2" s="17"/>
+      <c r="P2" s="17"/>
+      <c r="Q2" s="17"/>
+      <c r="R2" s="18"/>
     </row>
     <row r="3" spans="2:46" ht="50.1" customHeight="1">
-      <c r="B3" s="25" t="s">
+      <c r="B3" s="19" t="s">
         <v>4</v>
       </c>
-      <c r="C3" s="18" t="s">
+      <c r="C3" s="21" t="s">
         <v>5</v>
       </c>
-      <c r="D3" s="18" t="s">
+      <c r="D3" s="21" t="s">
         <v>0</v>
       </c>
-      <c r="E3" s="27" t="s">
+      <c r="E3" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="F3" s="27" t="s">
+      <c r="F3" s="22" t="s">
         <v>47</v>
       </c>
-      <c r="G3" s="18" t="s">
+      <c r="G3" s="21" t="s">
         <v>6</v>
       </c>
-      <c r="H3" s="18"/>
-      <c r="I3" s="18"/>
-      <c r="J3" s="18" t="s">
+      <c r="H3" s="21"/>
+      <c r="I3" s="21"/>
+      <c r="J3" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="K3" s="27" t="s">
+      <c r="K3" s="22" t="s">
         <v>8</v>
       </c>
-      <c r="L3" s="18" t="s">
+      <c r="L3" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="M3" s="18"/>
-      <c r="N3" s="19"/>
-      <c r="O3" s="20" t="s">
+      <c r="M3" s="21"/>
+      <c r="N3" s="27"/>
+      <c r="O3" s="28" t="s">
         <v>43</v>
       </c>
-      <c r="P3" s="18" t="s">
+      <c r="P3" s="21" t="s">
         <v>44</v>
       </c>
-      <c r="Q3" s="18" t="s">
+      <c r="Q3" s="21" t="s">
         <v>45</v>
       </c>
-      <c r="R3" s="18" t="s">
+      <c r="R3" s="21" t="s">
         <v>46</v>
       </c>
       <c r="S3" s="2"/>
@@ -1928,11 +1931,11 @@
       <c r="AT3" s="2"/>
     </row>
     <row r="4" spans="2:46" ht="33.200000000000003" customHeight="1">
-      <c r="B4" s="26"/>
-      <c r="C4" s="18"/>
-      <c r="D4" s="18"/>
-      <c r="E4" s="28"/>
-      <c r="F4" s="28"/>
+      <c r="B4" s="20"/>
+      <c r="C4" s="21"/>
+      <c r="D4" s="21"/>
+      <c r="E4" s="23"/>
+      <c r="F4" s="23"/>
       <c r="G4" s="13" t="s">
         <v>10</v>
       </c>
@@ -1942,8 +1945,8 @@
       <c r="I4" s="13" t="s">
         <v>71</v>
       </c>
-      <c r="J4" s="18"/>
-      <c r="K4" s="28"/>
+      <c r="J4" s="21"/>
+      <c r="K4" s="23"/>
       <c r="L4" s="1" t="s">
         <v>2</v>
       </c>
@@ -1953,10 +1956,10 @@
       <c r="N4" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="O4" s="20"/>
-      <c r="P4" s="20"/>
-      <c r="Q4" s="20"/>
-      <c r="R4" s="20"/>
+      <c r="O4" s="28"/>
+      <c r="P4" s="28"/>
+      <c r="Q4" s="28"/>
+      <c r="R4" s="28"/>
       <c r="S4" s="2"/>
       <c r="T4" s="2"/>
       <c r="U4" s="2"/>
@@ -1987,25 +1990,25 @@
       <c r="AT4" s="2"/>
     </row>
     <row r="5" spans="2:46" ht="50.1" customHeight="1">
-      <c r="B5" s="15" t="s">
+      <c r="B5" s="24" t="s">
         <v>30</v>
       </c>
-      <c r="C5" s="16"/>
-      <c r="D5" s="16"/>
-      <c r="E5" s="16"/>
-      <c r="F5" s="16"/>
-      <c r="G5" s="16"/>
-      <c r="H5" s="16"/>
-      <c r="I5" s="16"/>
-      <c r="J5" s="16"/>
-      <c r="K5" s="16"/>
-      <c r="L5" s="16"/>
-      <c r="M5" s="16"/>
-      <c r="N5" s="16"/>
-      <c r="O5" s="16"/>
-      <c r="P5" s="16"/>
-      <c r="Q5" s="16"/>
-      <c r="R5" s="17"/>
+      <c r="C5" s="25"/>
+      <c r="D5" s="25"/>
+      <c r="E5" s="25"/>
+      <c r="F5" s="25"/>
+      <c r="G5" s="25"/>
+      <c r="H5" s="25"/>
+      <c r="I5" s="25"/>
+      <c r="J5" s="25"/>
+      <c r="K5" s="25"/>
+      <c r="L5" s="25"/>
+      <c r="M5" s="25"/>
+      <c r="N5" s="25"/>
+      <c r="O5" s="25"/>
+      <c r="P5" s="25"/>
+      <c r="Q5" s="25"/>
+      <c r="R5" s="26"/>
     </row>
     <row r="6" spans="2:46" ht="90" customHeight="1">
       <c r="B6" s="3">
@@ -2350,10 +2353,10 @@
       </c>
       <c r="L12" s="7">
         <f t="shared" si="0"/>
-        <v>6318</v>
+        <v>8100</v>
       </c>
       <c r="M12" s="14">
-        <v>7020</v>
+        <v>9000</v>
       </c>
       <c r="N12" s="6">
         <v>0.1</v>
@@ -2402,10 +2405,10 @@
       </c>
       <c r="L13" s="7">
         <f t="shared" si="0"/>
-        <v>18252</v>
+        <v>23400</v>
       </c>
       <c r="M13" s="14">
-        <v>20280</v>
+        <v>26000</v>
       </c>
       <c r="N13" s="6">
         <v>0.1</v>
@@ -2633,6 +2636,12 @@
     </row>
   </sheetData>
   <mergeCells count="16">
+    <mergeCell ref="B5:R5"/>
+    <mergeCell ref="L3:N3"/>
+    <mergeCell ref="O3:O4"/>
+    <mergeCell ref="P3:P4"/>
+    <mergeCell ref="Q3:Q4"/>
+    <mergeCell ref="R3:R4"/>
     <mergeCell ref="B1:R1"/>
     <mergeCell ref="B2:R2"/>
     <mergeCell ref="B3:B4"/>
@@ -2643,12 +2652,6 @@
     <mergeCell ref="G3:I3"/>
     <mergeCell ref="J3:J4"/>
     <mergeCell ref="K3:K4"/>
-    <mergeCell ref="B5:R5"/>
-    <mergeCell ref="L3:N3"/>
-    <mergeCell ref="O3:O4"/>
-    <mergeCell ref="P3:P4"/>
-    <mergeCell ref="Q3:Q4"/>
-    <mergeCell ref="R3:R4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="10" orientation="portrait" r:id="rId1"/>
